--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_LETRA CORPOREA BARBASTRO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_LETRA CORPOREA BARBASTRO.xlsx
@@ -565,13 +565,13 @@
         <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>79.5438</v>
+        <v>71.3591</v>
       </c>
       <c r="E2" t="n">
-        <v>68.7414</v>
+        <v>65.20399999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>10.8029</v>
+        <v>6.1552</v>
       </c>
       <c r="G2" t="n">
         <v>32.224</v>
@@ -610,13 +610,13 @@
         <v>54.5558</v>
       </c>
       <c r="S2" t="n">
-        <v>15.7923</v>
+        <v>7.6075</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3161</v>
+        <v>-1.2215</v>
       </c>
       <c r="U2" t="n">
-        <v>13.4768</v>
+        <v>8.828900000000001</v>
       </c>
       <c r="V2" t="n">
         <v>48.5882</v>
@@ -643,13 +643,13 @@
         <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>30.7666</v>
+        <v>15.7449</v>
       </c>
       <c r="E3" t="n">
-        <v>33.7311</v>
+        <v>23.3977</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.9642</v>
+        <v>-7.652799999999999</v>
       </c>
       <c r="G3" t="n">
         <v>8.7751</v>
@@ -688,13 +688,13 @@
         <v>43.8429</v>
       </c>
       <c r="S3" t="n">
-        <v>22.7827</v>
+        <v>7.761</v>
       </c>
       <c r="T3" t="n">
-        <v>12.5805</v>
+        <v>2.2471</v>
       </c>
       <c r="U3" t="n">
-        <v>10.2025</v>
+        <v>5.5136</v>
       </c>
       <c r="V3" t="n">
         <v>-7.5362</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. ZICOVICH</t>
+          <t>T. SARTOR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>2.303700000000001</v>
+        <v>7.712599999999998</v>
       </c>
       <c r="E4" t="n">
-        <v>9.1768</v>
+        <v>9.0625</v>
       </c>
       <c r="F4" t="n">
-        <v>-6.8732</v>
+        <v>-1.3496</v>
       </c>
       <c r="G4" t="n">
-        <v>1.124</v>
+        <v>4.964899999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>4.7607</v>
+        <v>4.828000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.6365</v>
+        <v>0.1365000000000005</v>
       </c>
       <c r="J4" t="n">
-        <v>10.0218</v>
+        <v>40.7384</v>
       </c>
       <c r="K4" t="n">
-        <v>9.5067</v>
+        <v>28.4972</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5150000000000006</v>
+        <v>12.2412</v>
       </c>
       <c r="M4" t="n">
-        <v>-8.897599999999999</v>
+        <v>-35.7735</v>
       </c>
       <c r="N4" t="n">
-        <v>-4.746</v>
+        <v>-23.6694</v>
       </c>
       <c r="O4" t="n">
-        <v>-4.151800000000001</v>
+        <v>-12.1044</v>
       </c>
       <c r="P4" t="n">
-        <v>5.3563</v>
+        <v>-21.6237</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.9757</v>
+        <v>-66.4586</v>
       </c>
       <c r="R4" t="n">
-        <v>8.332000000000001</v>
+        <v>44.835</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7659</v>
+        <v>-0.7454000000000002</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9244000000000002</v>
+        <v>-1.0692</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8418000000000001</v>
+        <v>0.3238</v>
       </c>
       <c r="V4" t="n">
-        <v>-5.9429</v>
+        <v>25.117</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2065</v>
+        <v>35.8514</v>
       </c>
       <c r="X4" t="n">
-        <v>-7.1494</v>
+        <v>-10.7346</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. SARTOR</t>
+          <t>B. ZICOVICH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>2.013500000000001</v>
+        <v>0.7898000000000008</v>
       </c>
       <c r="E5" t="n">
-        <v>7.929</v>
+        <v>7.8958</v>
       </c>
       <c r="F5" t="n">
-        <v>-5.9152</v>
+        <v>-7.106100000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>4.964899999999999</v>
+        <v>1.124</v>
       </c>
       <c r="H5" t="n">
-        <v>4.828000000000001</v>
+        <v>4.7607</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1365000000000005</v>
+        <v>-3.6365</v>
       </c>
       <c r="J5" t="n">
-        <v>40.7384</v>
+        <v>10.0218</v>
       </c>
       <c r="K5" t="n">
-        <v>28.4972</v>
+        <v>9.5067</v>
       </c>
       <c r="L5" t="n">
-        <v>12.2412</v>
+        <v>0.5150000000000006</v>
       </c>
       <c r="M5" t="n">
-        <v>-35.7735</v>
+        <v>-8.897599999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>-23.6694</v>
+        <v>-4.746</v>
       </c>
       <c r="O5" t="n">
-        <v>-12.1044</v>
+        <v>-4.151800000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>-21.6237</v>
+        <v>5.3563</v>
       </c>
       <c r="Q5" t="n">
-        <v>-66.4586</v>
+        <v>-2.9757</v>
       </c>
       <c r="R5" t="n">
-        <v>44.835</v>
+        <v>8.332000000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>-6.4445</v>
+        <v>0.2521</v>
       </c>
       <c r="T5" t="n">
-        <v>-2.2025</v>
+        <v>-0.3568</v>
       </c>
       <c r="U5" t="n">
-        <v>-4.2419</v>
+        <v>0.6088</v>
       </c>
       <c r="V5" t="n">
-        <v>25.117</v>
+        <v>-5.9429</v>
       </c>
       <c r="W5" t="n">
-        <v>35.8514</v>
+        <v>1.2065</v>
       </c>
       <c r="X5" t="n">
-        <v>-10.7346</v>
+        <v>-7.1494</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.7828</v>
+        <v>-2.1547</v>
       </c>
       <c r="E6" t="n">
-        <v>-6.2676</v>
+        <v>-5.468400000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4847</v>
+        <v>3.3137</v>
       </c>
       <c r="G6" t="n">
         <v>-1.1819</v>
@@ -922,13 +922,13 @@
         <v>11.903</v>
       </c>
       <c r="S6" t="n">
-        <v>-3.7776</v>
+        <v>-2.1496</v>
       </c>
       <c r="T6" t="n">
-        <v>-2.6976</v>
+        <v>-1.8983</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.0803</v>
+        <v>-0.2513000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>2.1689</v>
@@ -955,13 +955,13 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.799500000000001</v>
+        <v>-2.541400000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6239000000000008</v>
+        <v>0.7486999999999995</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.4234</v>
+        <v>-3.29</v>
       </c>
       <c r="G7" t="n">
         <v>1.1563</v>
@@ -1000,13 +1000,13 @@
         <v>6.348199999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>-3.2745</v>
+        <v>-2.0166</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.4392</v>
+        <v>-1.3146</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.8353</v>
+        <v>-0.702</v>
       </c>
       <c r="V7" t="n">
         <v>3.4769</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. PARDINA CERESUELA</t>
+          <t>X. ROSÀS MARCO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>-14.6494</v>
+        <v>-7.265400000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7613999999999996</v>
+        <v>-9.6181</v>
       </c>
       <c r="F8" t="n">
-        <v>-15.4109</v>
+        <v>2.352599999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-13.1976</v>
+        <v>4.7125</v>
       </c>
       <c r="H8" t="n">
-        <v>-5.234999999999999</v>
+        <v>5.983199999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-7.963</v>
+        <v>-1.270999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>8.9312</v>
+        <v>34.7766</v>
       </c>
       <c r="K8" t="n">
-        <v>6.654299999999999</v>
+        <v>30.641</v>
       </c>
       <c r="L8" t="n">
-        <v>2.2774</v>
+        <v>4.1356</v>
       </c>
       <c r="M8" t="n">
-        <v>-22.1289</v>
+        <v>-30.0642</v>
       </c>
       <c r="N8" t="n">
-        <v>-11.8887</v>
+        <v>-24.6576</v>
       </c>
       <c r="O8" t="n">
-        <v>-10.2398</v>
+        <v>-5.4067</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5949999999999995</v>
+        <v>-11.9031</v>
       </c>
       <c r="Q8" t="n">
-        <v>-22.6156</v>
+        <v>-58.3249</v>
       </c>
       <c r="R8" t="n">
-        <v>23.2111</v>
+        <v>46.4221</v>
       </c>
       <c r="S8" t="n">
-        <v>9.1073</v>
+        <v>-1.2554</v>
       </c>
       <c r="T8" t="n">
-        <v>10.0289</v>
+        <v>-5.5299</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9214</v>
+        <v>4.2742</v>
       </c>
       <c r="V8" t="n">
-        <v>-11.1546</v>
+        <v>1.1809</v>
       </c>
       <c r="W8" t="n">
-        <v>4.4175</v>
+        <v>19.46</v>
       </c>
       <c r="X8" t="n">
-        <v>-15.5719</v>
+        <v>-18.2793</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X. ROSÀS MARCO</t>
+          <t>C. DIOP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>-17.5807</v>
+        <v>-20.0266</v>
       </c>
       <c r="E9" t="n">
-        <v>-16.8338</v>
+        <v>-13.2093</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7470000000000003</v>
+        <v>-6.8172</v>
       </c>
       <c r="G9" t="n">
-        <v>4.7125</v>
+        <v>-7.8982</v>
       </c>
       <c r="H9" t="n">
-        <v>5.983199999999999</v>
+        <v>-5.672700000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.270999999999999</v>
+        <v>-2.2253</v>
       </c>
       <c r="J9" t="n">
-        <v>34.7766</v>
+        <v>1.5483</v>
       </c>
       <c r="K9" t="n">
-        <v>30.641</v>
+        <v>-1.9908</v>
       </c>
       <c r="L9" t="n">
-        <v>4.1356</v>
+        <v>3.5394</v>
       </c>
       <c r="M9" t="n">
-        <v>-30.0642</v>
+        <v>-9.447000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-24.6576</v>
+        <v>-3.6821</v>
       </c>
       <c r="O9" t="n">
-        <v>-5.4067</v>
+        <v>-5.7649</v>
       </c>
       <c r="P9" t="n">
-        <v>-11.9031</v>
+        <v>-5.356300000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>-58.3249</v>
+        <v>-14.8787</v>
       </c>
       <c r="R9" t="n">
-        <v>46.4221</v>
+        <v>9.522499999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>-11.5713</v>
+        <v>-0.5669000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-12.7454</v>
+        <v>-1.0142</v>
       </c>
       <c r="U9" t="n">
-        <v>1.1744</v>
+        <v>0.4473999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>1.1809</v>
+        <v>-6.205</v>
       </c>
       <c r="W9" t="n">
-        <v>19.46</v>
+        <v>1.1352</v>
       </c>
       <c r="X9" t="n">
-        <v>-18.2793</v>
+        <v>-7.340199999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. DIOP</t>
+          <t>J. PARDINA CERESUELA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>-19.6071</v>
+        <v>-21.5389</v>
       </c>
       <c r="E10" t="n">
-        <v>-12.5177</v>
+        <v>-8.1488</v>
       </c>
       <c r="F10" t="n">
-        <v>-7.0894</v>
+        <v>-13.39</v>
       </c>
       <c r="G10" t="n">
-        <v>-7.8982</v>
+        <v>-13.1976</v>
       </c>
       <c r="H10" t="n">
-        <v>-5.672700000000001</v>
+        <v>-5.234999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.2253</v>
+        <v>-7.963</v>
       </c>
       <c r="J10" t="n">
-        <v>1.5483</v>
+        <v>8.9312</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.9908</v>
+        <v>6.654299999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>3.5394</v>
+        <v>2.2774</v>
       </c>
       <c r="M10" t="n">
-        <v>-9.447000000000001</v>
+        <v>-22.1289</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.6821</v>
+        <v>-11.8887</v>
       </c>
       <c r="O10" t="n">
-        <v>-5.7649</v>
+        <v>-10.2398</v>
       </c>
       <c r="P10" t="n">
-        <v>-5.356300000000001</v>
+        <v>0.5949999999999995</v>
       </c>
       <c r="Q10" t="n">
-        <v>-14.8787</v>
+        <v>-22.6156</v>
       </c>
       <c r="R10" t="n">
-        <v>9.522499999999999</v>
+        <v>23.2111</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1475</v>
+        <v>2.2177</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3227</v>
+        <v>1.1176</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1751</v>
+        <v>1.0999</v>
       </c>
       <c r="V10" t="n">
-        <v>-6.205</v>
+        <v>-11.1546</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1352</v>
+        <v>4.4175</v>
       </c>
       <c r="X10" t="n">
-        <v>-7.340199999999999</v>
+        <v>-15.5719</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. GER SIERRA</t>
+          <t>A. FERNANDEZ FUERTES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D11" t="n">
-        <v>-34.0992</v>
+        <v>-22.9006</v>
       </c>
       <c r="E11" t="n">
-        <v>-23.3235</v>
+        <v>-12.566</v>
       </c>
       <c r="F11" t="n">
-        <v>-10.776</v>
+        <v>-10.3345</v>
       </c>
       <c r="G11" t="n">
-        <v>-11.1286</v>
+        <v>-31.0769</v>
       </c>
       <c r="H11" t="n">
-        <v>-7.7331</v>
+        <v>-24.4487</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.3958</v>
+        <v>-6.627799999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>7.4819</v>
+        <v>8.2155</v>
       </c>
       <c r="K11" t="n">
-        <v>3.5195</v>
+        <v>0.7890999999999997</v>
       </c>
       <c r="L11" t="n">
-        <v>3.9622</v>
+        <v>7.4265</v>
       </c>
       <c r="M11" t="n">
-        <v>-18.6104</v>
+        <v>-39.2923</v>
       </c>
       <c r="N11" t="n">
-        <v>-11.2528</v>
+        <v>-25.2378</v>
       </c>
       <c r="O11" t="n">
-        <v>-7.3576</v>
+        <v>-14.0541</v>
       </c>
       <c r="P11" t="n">
-        <v>-4.9598</v>
+        <v>13.2919</v>
       </c>
       <c r="Q11" t="n">
-        <v>-24.7976</v>
+        <v>-32.9314</v>
       </c>
       <c r="R11" t="n">
-        <v>19.8386</v>
+        <v>46.2235</v>
       </c>
       <c r="S11" t="n">
-        <v>-7.7166</v>
+        <v>-7.0609</v>
       </c>
       <c r="T11" t="n">
-        <v>-6.007099999999999</v>
+        <v>-3.852</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.7095</v>
+        <v>-3.2091</v>
       </c>
       <c r="V11" t="n">
-        <v>-10.2946</v>
+        <v>1.9456</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>16.0021</v>
       </c>
       <c r="X11" t="n">
-        <v>-10.2946</v>
+        <v>-14.0565</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ FUERTES</t>
+          <t>R. GER SIERRA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D12" t="n">
-        <v>-37.2266</v>
+        <v>-30.1948</v>
       </c>
       <c r="E12" t="n">
-        <v>-19.4135</v>
+        <v>-21.6854</v>
       </c>
       <c r="F12" t="n">
-        <v>-17.8135</v>
+        <v>-8.509500000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>-31.0769</v>
+        <v>-11.1286</v>
       </c>
       <c r="H12" t="n">
-        <v>-24.4487</v>
+        <v>-7.7331</v>
       </c>
       <c r="I12" t="n">
-        <v>-6.627799999999999</v>
+        <v>-3.3958</v>
       </c>
       <c r="J12" t="n">
-        <v>8.2155</v>
+        <v>7.4819</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7890999999999997</v>
+        <v>3.5195</v>
       </c>
       <c r="L12" t="n">
-        <v>7.4265</v>
+        <v>3.9622</v>
       </c>
       <c r="M12" t="n">
-        <v>-39.2923</v>
+        <v>-18.6104</v>
       </c>
       <c r="N12" t="n">
-        <v>-25.2378</v>
+        <v>-11.2528</v>
       </c>
       <c r="O12" t="n">
-        <v>-14.0541</v>
+        <v>-7.3576</v>
       </c>
       <c r="P12" t="n">
-        <v>13.2919</v>
+        <v>-4.9598</v>
       </c>
       <c r="Q12" t="n">
-        <v>-32.9314</v>
+        <v>-24.7976</v>
       </c>
       <c r="R12" t="n">
-        <v>46.2235</v>
+        <v>19.8386</v>
       </c>
       <c r="S12" t="n">
-        <v>-21.3873</v>
+        <v>-3.8118</v>
       </c>
       <c r="T12" t="n">
-        <v>-10.6989</v>
+        <v>-4.3691</v>
       </c>
       <c r="U12" t="n">
-        <v>-10.6882</v>
+        <v>0.5572999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>1.9456</v>
+        <v>-10.2946</v>
       </c>
       <c r="W12" t="n">
-        <v>16.0021</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-14.0565</v>
+        <v>-10.2946</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>21</v>
       </c>
       <c r="D13" t="n">
-        <v>-49.4162</v>
+        <v>-39.1046</v>
       </c>
       <c r="E13" t="n">
-        <v>-35.7451</v>
+        <v>-29.5952</v>
       </c>
       <c r="F13" t="n">
-        <v>-13.6705</v>
+        <v>-9.508799999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-28.8057</v>
@@ -1468,13 +1468,13 @@
         <v>35.3123</v>
       </c>
       <c r="S13" t="n">
-        <v>-10.8459</v>
+        <v>-0.5338999999999998</v>
       </c>
       <c r="T13" t="n">
-        <v>-10.7617</v>
+        <v>-4.6116</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.08400000000000041</v>
+        <v>4.0777</v>
       </c>
       <c r="V13" t="n">
         <v>-11.9468</v>
@@ -1501,13 +1501,13 @@
         <v>18</v>
       </c>
       <c r="D14" t="n">
-        <v>-49.71599999999999</v>
+        <v>-43.7725</v>
       </c>
       <c r="E14" t="n">
-        <v>-38.3179</v>
+        <v>-31.7597</v>
       </c>
       <c r="F14" t="n">
-        <v>-11.398</v>
+        <v>-12.0128</v>
       </c>
       <c r="G14" t="n">
         <v>-27.7957</v>
@@ -1546,13 +1546,13 @@
         <v>26.5835</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.7383</v>
+        <v>0.2052999999999998</v>
       </c>
       <c r="T14" t="n">
-        <v>-9.050599999999999</v>
+        <v>-2.4926</v>
       </c>
       <c r="U14" t="n">
-        <v>3.3124</v>
+        <v>2.6978</v>
       </c>
       <c r="V14" t="n">
         <v>-2.4935</v>
@@ -1579,13 +1579,13 @@
         <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>-115.2499</v>
+        <v>-93.8931</v>
       </c>
       <c r="E15" t="n">
-        <v>-31.4555</v>
+        <v>-25.7422</v>
       </c>
       <c r="F15" t="n">
-        <v>-83.7937</v>
+        <v>-68.1498</v>
       </c>
       <c r="G15" t="n">
         <v>-68.12779999999999</v>
@@ -1624,13 +1624,13 @@
         <v>376.9305</v>
       </c>
       <c r="S15" t="n">
-        <v>-21.4553</v>
+        <v>-0.09689999999999821</v>
       </c>
       <c r="T15" t="n">
-        <v>-30.0758</v>
+        <v>-24.3651</v>
       </c>
       <c r="U15" t="n">
-        <v>8.622399999999995</v>
+        <v>24.26700000000001</v>
       </c>
       <c r="V15" t="n">
         <v>26.9039</v>
